--- a/data/trans_camb/P2A_fisi_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 4,22</t>
+          <t>-2,38; 4,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 0,7</t>
+          <t>-4,97; 0,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 6,74</t>
+          <t>-1,67; 6,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,28</t>
+          <t>-1,82; 3,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 1,88</t>
+          <t>-3,15; 1,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 1,24</t>
+          <t>-3,14; 1,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,14</t>
+          <t>-1,04; 3,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 0,7</t>
+          <t>-2,6; 0,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 3,34</t>
+          <t>-1,22; 3,32</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-74,06; —</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>-100,0; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-57,1; 883,36</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-65,45; 770,88</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,35; 710,6</t>
+          <t>-70,9; 884,03</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 5,29</t>
+          <t>-0,06; 5,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 3,35</t>
+          <t>-0,9; 3,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 5,32</t>
+          <t>0,11; 5,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 1,95</t>
+          <t>-4,13; 1,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 0,08</t>
+          <t>-5,28; -0,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 3,79</t>
+          <t>-3,31; 3,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 2,72</t>
+          <t>-1,44; 2,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 0,9</t>
+          <t>-2,53; 0,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 3,55</t>
+          <t>-0,82; 3,48</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-49,68; —</t>
+          <t>-45,58; 1602,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,37 +1009,37 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-24,38; 2197,17</t>
+          <t>-41,03; 1452,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-72,61; 91,12</t>
+          <t>-75,16; 93,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-90,84; 14,46</t>
+          <t>-89,57; 7,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,5; 177,77</t>
+          <t>-63,01; 143,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,65; 166,55</t>
+          <t>-45,33; 167,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,17; 65,88</t>
+          <t>-72,07; 51,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-31,07; 223,45</t>
+          <t>-29,18; 217,24</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,84</t>
+          <t>-2,02; 2,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 5,47</t>
+          <t>-0,34; 5,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 6,66</t>
+          <t>0,45; 6,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 1,97</t>
+          <t>-7,36; 1,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,39; -0,44</t>
+          <t>-8,57; -0,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 5,42</t>
+          <t>-4,15; 5,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 1,76</t>
+          <t>-4,23; 1,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 1,64</t>
+          <t>-3,72; 1,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 5,22</t>
+          <t>-0,72; 4,96</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-90,6; 82,44</t>
+          <t>-90,25; 87,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-96,15; 23,01</t>
+          <t>-100,0; 11,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,45; 210,81</t>
+          <t>-53,2; 159,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-80,32; 120,91</t>
+          <t>-82,81; 69,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-71,91; 108,22</t>
+          <t>-70,96; 79,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-20,95; 326,46</t>
+          <t>-18,51; 256,62</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 3,6</t>
+          <t>-3,52; 3,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 5,97</t>
+          <t>-2,64; 5,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 6,88</t>
+          <t>-0,23; 7,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 8,09</t>
+          <t>-0,47; 8,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 7,46</t>
+          <t>-1,67; 6,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 10,45</t>
+          <t>0,89; 10,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 4,97</t>
+          <t>-0,57; 5,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 5,05</t>
+          <t>-0,91; 4,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,73; 7,63</t>
+          <t>1,58; 7,64</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-72,2; 236,8</t>
+          <t>-79,51; 214,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-59,96; 414,79</t>
+          <t>-59,54; 336,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 399,61</t>
+          <t>-8,92; 434,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 483,83</t>
+          <t>-23,53; 528,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-45,79; 417,25</t>
+          <t>-50,73; 430,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,94; 708,49</t>
+          <t>-0,49; 650,59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,21; 255,85</t>
+          <t>-16,36; 255,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-37,3; 223,36</t>
+          <t>-27,26; 238,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33,27; 394,9</t>
+          <t>27,69; 369,27</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,63</t>
+          <t>-0,48; 2,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,38</t>
+          <t>-0,54; 2,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,31</t>
+          <t>1,63; 5,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,01</t>
+          <t>-1,6; 2,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 0,43</t>
+          <t>-2,81; 0,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,89</t>
+          <t>0,5; 4,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,79</t>
+          <t>-0,67; 1,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,91</t>
+          <t>-1,29; 0,97</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,44</t>
+          <t>1,62; 4,55</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-27,65; 226,97</t>
+          <t>-23,61; 226,94</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-30,98; 213,54</t>
+          <t>-22,92; 227,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>61,9; 479,42</t>
+          <t>57,82; 471,35</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-36,62; 83,57</t>
+          <t>-38,18; 78,49</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-64,85; 20,28</t>
+          <t>-65,35; 21,11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,16; 184,63</t>
+          <t>8,32; 192,01</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 85,41</t>
+          <t>-21,31; 86,76</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-40,84; 44,8</t>
+          <t>-41,62; 48,6</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>48,08; 211,19</t>
+          <t>46,81; 224,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_fisi_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 4,79</t>
+          <t>-2,58; 4,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 0,75</t>
+          <t>-4,75; 0,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 6,96</t>
+          <t>-1,6; 6,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 3,22</t>
+          <t>-1,77; 3,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,46</t>
+          <t>-2,47; 1,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 1,25</t>
+          <t>-3,13; 1,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 3,3</t>
+          <t>-1,12; 3,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 0,71</t>
+          <t>-2,75; 0,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,32</t>
+          <t>-1,13; 3,66</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-74,06; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-70,59; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-57,1; 883,36</t>
+          <t>-61,2; 740,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-70,9; 884,03</t>
+          <t>-71,79; —</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 5,37</t>
+          <t>-0,04; 5,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 3,58</t>
+          <t>-1,18; 3,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 5,32</t>
+          <t>0,25; 5,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 1,93</t>
+          <t>-4,06; 2,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,28; -0,16</t>
+          <t>-5,5; -0,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 3,71</t>
+          <t>-3,32; 3,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 2,76</t>
+          <t>-1,46; 2,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 0,71</t>
+          <t>-2,59; 0,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 3,48</t>
+          <t>-0,76; 3,59</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-45,58; 1602,98</t>
+          <t>-55,93; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,37 +1009,37 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,03; 1452,64</t>
+          <t>-26,37; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-75,16; 93,49</t>
+          <t>-72,91; 101,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-89,57; 7,53</t>
+          <t>-90,53; 8,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,01; 143,09</t>
+          <t>-62,81; 163,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,33; 167,29</t>
+          <t>-45,2; 178,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-72,07; 51,49</t>
+          <t>-72,06; 79,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-29,18; 217,24</t>
+          <t>-27,19; 230,43</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,85</t>
+          <t>-2,23; 2,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 5,48</t>
+          <t>-0,46; 5,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 6,86</t>
+          <t>0,11; 6,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 1,58</t>
+          <t>-7,18; 2,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,57; -0,69</t>
+          <t>-8,67; -0,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 5,13</t>
+          <t>-4,36; 5,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 1,22</t>
+          <t>-4,14; 1,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 1,33</t>
+          <t>-3,5; 1,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,96</t>
+          <t>-0,89; 4,98</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-90,25; 87,02</t>
+          <t>-87,27; 102,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 11,36</t>
+          <t>-100,0; 16,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-53,2; 159,25</t>
+          <t>-53,45; 197,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-82,81; 69,4</t>
+          <t>-83,95; 87,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-70,96; 79,7</t>
+          <t>-70,96; 101,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 256,62</t>
+          <t>-21,07; 270,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 3,76</t>
+          <t>-3,5; 3,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 5,8</t>
+          <t>-2,45; 5,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 7,08</t>
+          <t>-0,14; 7,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 8,2</t>
+          <t>-0,67; 7,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 6,89</t>
+          <t>-1,74; 7,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 10,34</t>
+          <t>1,07; 9,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 5,06</t>
+          <t>-0,59; 4,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 4,61</t>
+          <t>-0,79; 5,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 7,64</t>
+          <t>1,76; 7,4</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-79,51; 214,07</t>
+          <t>-75,47; 273,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-59,54; 336,89</t>
+          <t>-63,6; 422,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 434,91</t>
+          <t>-9,34; 413,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 528,25</t>
+          <t>-21,84; 441,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,73; 430,1</t>
+          <t>-47,37; 548,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 650,59</t>
+          <t>8,12; 555,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 255,91</t>
+          <t>-19,18; 232,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,26; 238,29</t>
+          <t>-22,35; 250,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>27,69; 369,27</t>
+          <t>37,64; 356,71</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,69</t>
+          <t>-0,43; 2,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 2,43</t>
+          <t>-0,57; 2,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,06</t>
+          <t>1,78; 5,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,02</t>
+          <t>-1,73; 2,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 0,42</t>
+          <t>-2,96; 0,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,98</t>
+          <t>0,62; 5,04</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,69</t>
+          <t>-0,58; 1,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,97</t>
+          <t>-1,33; 0,95</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,55</t>
+          <t>1,68; 4,47</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 226,94</t>
+          <t>-21,71; 250,46</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 227,7</t>
+          <t>-27,8; 207,92</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>57,82; 471,35</t>
+          <t>60,79; 451,16</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-38,18; 78,49</t>
+          <t>-41,21; 81,66</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-65,35; 21,11</t>
+          <t>-67,88; 22,89</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,32; 192,01</t>
+          <t>12,54; 202,87</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-21,31; 86,76</t>
+          <t>-18,64; 97,96</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-41,62; 48,6</t>
+          <t>-41,2; 46,21</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>46,81; 224,96</t>
+          <t>51,97; 211,4</t>
         </is>
       </c>
     </row>
